--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1727-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1727-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{694C8F9F-EED3-4E88-B8C5-E69A8BBA5325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E2E7720-9094-4D57-9207-F8DD2BFA3C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{FEA60913-56B0-43EF-A1AA-70627B3D6F71}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C7E60CED-E204-4C82-BA84-5296B067457F}"/>
   </bookViews>
   <sheets>
     <sheet name="1727-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1586,29 +1586,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457890E3-C3E8-470D-B41E-881815981C98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D58A44CA-0E5B-452D-B7FF-D7DA450292A6}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1641,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1678,7 +1677,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1730,7 +1729,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1798,7 +1797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1942,7 +1941,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2014,7 +2013,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2086,7 +2085,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2230,7 +2229,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>2018</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2017</v>
       </c>
@@ -2374,7 +2373,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2016</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2015</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2012</v>
       </c>
@@ -2734,7 +2733,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2011</v>
       </c>
@@ -2806,7 +2805,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="43">
         <v>2010</v>
       </c>
@@ -2878,7 +2877,7 @@
         <v>9.86</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="45"/>
       <c r="B20" s="46"/>
       <c r="C20" s="20" t="s">
@@ -2906,7 +2905,7 @@
       <c r="W20" s="54"/>
       <c r="X20" s="48"/>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="55">
         <v>2009</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="57"/>
       <c r="B22" s="58"/>
       <c r="C22" s="22" t="s">
@@ -3006,7 +3005,7 @@
       <c r="W22" s="64"/>
       <c r="X22" s="60"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="43">
         <v>2008</v>
       </c>
@@ -3078,7 +3077,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="20" t="s">
@@ -3106,7 +3105,7 @@
       <c r="W24" s="54"/>
       <c r="X24" s="48"/>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2007</v>
       </c>
@@ -3178,7 +3177,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2006</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="55">
         <v>2005</v>
       </c>
@@ -3322,7 +3321,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="57"/>
       <c r="B28" s="58"/>
       <c r="C28" s="22" t="s">
@@ -3350,7 +3349,7 @@
       <c r="W28" s="64"/>
       <c r="X28" s="60"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2004</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="55">
         <v>2003</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="57"/>
       <c r="B31" s="58"/>
       <c r="C31" s="22" t="s">
@@ -3522,7 +3521,7 @@
       <c r="W31" s="64"/>
       <c r="X31" s="60"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="43">
         <v>2002</v>
       </c>
@@ -3594,7 +3593,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="45"/>
       <c r="B33" s="46"/>
       <c r="C33" s="20" t="s">
@@ -3622,7 +3621,7 @@
       <c r="W33" s="54"/>
       <c r="X33" s="48"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>2001</v>
       </c>
@@ -3694,7 +3693,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2000</v>
       </c>
@@ -3766,7 +3765,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>1999</v>
       </c>
@@ -3838,7 +3837,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1998</v>
       </c>
@@ -3910,7 +3909,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1997</v>
       </c>
@@ -3982,7 +3981,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1996</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>1995</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1994</v>
       </c>
@@ -4198,7 +4197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>1993</v>
       </c>
@@ -4270,7 +4269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1989</v>
       </c>
@@ -4342,7 +4341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1988</v>
       </c>
@@ -4414,7 +4413,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1987</v>
       </c>
@@ -4486,7 +4485,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>1986</v>
       </c>
@@ -4558,7 +4557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>1985</v>
       </c>
@@ -4630,7 +4629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>1979</v>
       </c>
@@ -4702,7 +4701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>1978</v>
       </c>
@@ -4774,7 +4773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="41">
         <v>1976</v>
       </c>
@@ -4846,7 +4845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>1974</v>
       </c>
@@ -4918,7 +4917,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="41">
         <v>1972</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="39" t="s">
         <v>60</v>
       </c>
